--- a/test_invoices/TEST_Bulk_Invoices.xlsx
+++ b/test_invoices/TEST_Bulk_Invoices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,252 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CDS-INV-99002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Continental Drayage Solutions</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CDS25051703</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MSCU7708219</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MEDUSV80290002</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>40HC</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Savannah — Garden City</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NewAge Monee IL</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>DRY</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N4" t="n">
+        <v>261</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Chassis day x 3</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1801</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Net 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PCD-INV-99005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pacific Coastline Drayage</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PCD25051803</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ONEU3344556</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ONEYSZPG60270005</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>40HC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Long Beach — Pier J</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NewAge Perris CA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>DRY</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>475</v>
+      </c>
+      <c r="L5" t="n">
+        <v>475</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Pier Pass</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>609.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Net 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACS-INV-99003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Atlantic Container Services</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ACS25051804</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HLBU2299881</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HLCUEC123789</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>40HC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Charleston — Wando Welch</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NewAge Monee IL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DRY</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N6" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Chassis day</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1555.4</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>Net 30</t>
         </is>
